--- a/Diplomarbeit/Zeiterfassung/Stundenaufzeichnung_Baumann_final.xlsx
+++ b/Diplomarbeit/Zeiterfassung/Stundenaufzeichnung_Baumann_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ch_ba\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HTL\HTL 5\Diplomarbeit_Sicherung_Privat\Diplomarbeit\Zeiterfassung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1B9471-2B46-4D49-BBCA-03FF2CA10C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F794AD70-EB97-49F0-9B6D-08493BA7D4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="23980" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stundenaufzeichnung" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="260">
   <si>
     <t>STUNDENAUFZEICHNUNG – DIPLOMARBEIT</t>
   </si>
@@ -228,9 +228,6 @@
     <t>30.10.2025</t>
   </si>
   <si>
-    <t>Neue Komponenten nach Sponsor-Vorgaben recherchiert; Victron-Vergleich</t>
-  </si>
-  <si>
     <t>Meilenstein: PV-System geplant und dokumentiert, Batterietechnik-Analyse erstellt – physischer Aufbau ausstehend (Komponenten vom Sponsor noch nicht übergeben)  (15.11.2025)</t>
   </si>
   <si>
@@ -498,9 +495,6 @@
     <t>19:30 – 21:00</t>
   </si>
   <si>
-    <t>Besprechung Sponsor (90 Min.) – keine Übergabe; neue Aufgaben notiert</t>
-  </si>
-  <si>
     <t>30.01.2026</t>
   </si>
   <si>
@@ -564,33 +558,18 @@
     <t>09:30 – 12:00</t>
   </si>
   <si>
-    <t>Kap. 4.7 Wirtschaftlichkeitsanalyse – aktuelle Strompreise eingearbeitet</t>
-  </si>
-  <si>
     <t>09.02.2026</t>
   </si>
   <si>
-    <t>Kap. 4.7 – Überarbeitung; Marktdaten &amp; Preisvergleiche</t>
-  </si>
-  <si>
     <t>10.02.2026</t>
   </si>
   <si>
-    <t>Kap. 4.8 – 1. Fassung; Monitoring &amp; Steuerung recherchiert</t>
-  </si>
-  <si>
     <t>11.02.2026</t>
   </si>
   <si>
-    <t>Kap. 4.9 – 1. Fassung; Gesamtsystem &amp; Integration beschrieben</t>
-  </si>
-  <si>
     <t>12.02.2026</t>
   </si>
   <si>
-    <t>Kap. 4.7–4.9 Gesamtkontrolle; Kapitel abgestimmt</t>
-  </si>
-  <si>
     <t>13.02.2026</t>
   </si>
   <si>
@@ -702,45 +681,15 @@
     <t>Abklärung Prof. Klotz – verfügbare Professoren für Schrank-Arbeiten</t>
   </si>
   <si>
-    <t>19:45 – 21:45</t>
-  </si>
-  <si>
     <t>Praktische Arbeit Schrank</t>
   </si>
   <si>
-    <t>Bohrungen Schrank; Befestigungsschienen montiert; Kabelkanäle vorbereitet</t>
-  </si>
-  <si>
-    <t>17.03.2026</t>
-  </si>
-  <si>
-    <t>17:30 – 20:30</t>
-  </si>
-  <si>
     <t>Bohrungen Schrank; Verkabelung &amp; Kabelführung geplant</t>
   </si>
   <si>
-    <t>23.03.2026</t>
-  </si>
-  <si>
-    <t>Bohrungen Schrank; Montagepunkte vorbereitet; erste Komponenten eingebaut</t>
-  </si>
-  <si>
     <t>25.03.2026</t>
   </si>
   <si>
-    <t>19:00 – 22:00</t>
-  </si>
-  <si>
-    <t>Abschlussarbeiten Schrank; Verbindungen geprüft; Verkabelung kontrolliert</t>
-  </si>
-  <si>
-    <t>22:15 – 23:45</t>
-  </si>
-  <si>
-    <t>Schlusskapitel &amp; Zusammenfassung geschrieben; Einleitung finalisiert</t>
-  </si>
-  <si>
     <t>Meilenstein: Finalisierung – Korrektur, Layout, Druck und Abgabe  (25.03.2026)</t>
   </si>
   <si>
@@ -817,6 +766,54 @@
   </si>
   <si>
     <t>Stunden</t>
+  </si>
+  <si>
+    <t>15:00 – 17:00</t>
+  </si>
+  <si>
+    <t>13:20 – 15:20</t>
+  </si>
+  <si>
+    <t>14:10 – 17:10</t>
+  </si>
+  <si>
+    <t>22:00 – 23:30</t>
+  </si>
+  <si>
+    <t>08:00 – 12:00</t>
+  </si>
+  <si>
+    <t>Verkabelung</t>
+  </si>
+  <si>
+    <t>Schlusskapitel &amp; Zusammenfassung geschrieben finalisiert</t>
+  </si>
+  <si>
+    <t>Bohrungen Schrank; Montagepunkte vorbereitet; Komponenten eingebaut</t>
+  </si>
+  <si>
+    <t>Bohrungen Schrank</t>
+  </si>
+  <si>
+    <t>Kap. 4.7–4.9</t>
+  </si>
+  <si>
+    <t>Kap. 4.9 – 1. Fassung</t>
+  </si>
+  <si>
+    <t>Kap. 4.8 – 1. Fassung</t>
+  </si>
+  <si>
+    <t>Kap. 4.7 – Überarbeitung</t>
+  </si>
+  <si>
+    <t>Kap. 4.7 Wirtschaftlichkeitsanalyse</t>
+  </si>
+  <si>
+    <t>Besprechung Sponsor  – keine Übergabe; neue Aufgaben notiert</t>
+  </si>
+  <si>
+    <t>Neue Komponenten nach Sponsor-Vorgaben recherchiert; Victron</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1103,10 +1100,34 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1116,32 +1137,14 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1459,7 +1462,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="33"/>
@@ -1469,7 +1472,7 @@
       <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="33"/>
@@ -1495,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -1699,7 +1702,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="34" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="33"/>
@@ -1789,7 +1792,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="34" t="s">
         <v>53</v>
       </c>
       <c r="B19" s="33"/>
@@ -1872,15 +1875,15 @@
         <v>20</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>64</v>
+        <v>259</v>
       </c>
       <c r="F23" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="32" t="s">
-        <v>65</v>
+      <c r="A24" s="34" t="s">
+        <v>64</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="33"/>
@@ -1893,7 +1896,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>23</v>
@@ -1902,7 +1905,7 @@
         <v>20</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="F25" s="10">
         <v>2</v>
@@ -1913,16 +1916,16 @@
         <v>20</v>
       </c>
       <c r="B26" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>70</v>
       </c>
       <c r="F26" s="13">
         <v>1.07</v>
@@ -1933,16 +1936,16 @@
         <v>21</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="D27" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>72</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>73</v>
       </c>
       <c r="F27" s="13">
         <v>0.08</v>
@@ -1953,16 +1956,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="D28" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="F28" s="13">
         <v>1.18</v>
@@ -1973,7 +1976,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>26</v>
@@ -1982,7 +1985,7 @@
         <v>20</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F29" s="10">
         <v>4</v>
@@ -1993,7 +1996,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>26</v>
@@ -2002,7 +2005,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F30" s="10">
         <v>4</v>
@@ -2013,16 +2016,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="D31" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>83</v>
       </c>
       <c r="F31" s="13">
         <v>1.25</v>
@@ -2033,7 +2036,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>58</v>
@@ -2042,7 +2045,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F32" s="10">
         <v>3.5</v>
@@ -2053,16 +2056,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="D33" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>88</v>
       </c>
       <c r="F33" s="10">
         <v>2.5</v>
@@ -2073,7 +2076,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>26</v>
@@ -2082,7 +2085,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F34" s="10">
         <v>4</v>
@@ -2093,7 +2096,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>55</v>
@@ -2102,7 +2105,7 @@
         <v>20</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F35" s="10">
         <v>2.5</v>
@@ -2113,7 +2116,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>26</v>
@@ -2122,7 +2125,7 @@
         <v>9</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F36" s="4">
         <v>4</v>
@@ -2133,7 +2136,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>48</v>
@@ -2142,7 +2145,7 @@
         <v>20</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F37" s="10">
         <v>2.5</v>
@@ -2153,16 +2156,16 @@
         <v>32</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F38" s="4">
         <v>2.5</v>
@@ -2173,16 +2176,16 @@
         <v>33</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="D39" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>102</v>
       </c>
       <c r="F39" s="13">
         <v>0.08</v>
@@ -2193,24 +2196,24 @@
         <v>34</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>104</v>
       </c>
       <c r="F40" s="13">
         <v>1.25</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="32" t="s">
-        <v>105</v>
+      <c r="A41" s="34" t="s">
+        <v>104</v>
       </c>
       <c r="B41" s="33"/>
       <c r="C41" s="33"/>
@@ -2223,7 +2226,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>61</v>
@@ -2232,7 +2235,7 @@
         <v>20</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F42" s="10">
         <v>3</v>
@@ -2243,7 +2246,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>61</v>
@@ -2252,7 +2255,7 @@
         <v>20</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F43" s="10">
         <v>5</v>
@@ -2263,16 +2266,16 @@
         <v>37</v>
       </c>
       <c r="B44" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>111</v>
       </c>
       <c r="F44" s="10">
         <v>2.5</v>
@@ -2283,16 +2286,16 @@
         <v>38</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F45" s="13">
         <v>0.08</v>
@@ -2303,7 +2306,7 @@
         <v>39</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>61</v>
@@ -2312,7 +2315,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F46" s="10">
         <v>3</v>
@@ -2323,16 +2326,16 @@
         <v>40</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>116</v>
       </c>
       <c r="F47" s="10">
         <v>2.5</v>
@@ -2343,16 +2346,16 @@
         <v>41</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="F48" s="13">
         <v>0.08</v>
@@ -2363,16 +2366,16 @@
         <v>42</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="D49" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="F49" s="13">
         <v>0.08</v>
@@ -2383,16 +2386,16 @@
         <v>43</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>123</v>
       </c>
       <c r="F50" s="13">
         <v>0.08</v>
@@ -2403,7 +2406,7 @@
         <v>44</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>61</v>
@@ -2412,7 +2415,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F51" s="10">
         <v>3</v>
@@ -2423,16 +2426,16 @@
         <v>45</v>
       </c>
       <c r="B52" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="D52" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>128</v>
       </c>
       <c r="F52" s="13">
         <v>1.05</v>
@@ -2443,16 +2446,16 @@
         <v>46</v>
       </c>
       <c r="B53" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="D53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>130</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>131</v>
       </c>
       <c r="F53" s="10">
         <v>2</v>
@@ -2463,16 +2466,16 @@
         <v>47</v>
       </c>
       <c r="B54" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="D54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>134</v>
       </c>
       <c r="F54" s="10">
         <v>2.5</v>
@@ -2483,16 +2486,16 @@
         <v>48</v>
       </c>
       <c r="B55" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>136</v>
       </c>
       <c r="F55" s="10">
         <v>2.5</v>
@@ -2503,16 +2506,16 @@
         <v>49</v>
       </c>
       <c r="B56" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>138</v>
       </c>
       <c r="F56" s="13">
         <v>0.08</v>
@@ -2523,7 +2526,7 @@
         <v>50</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>61</v>
@@ -2532,7 +2535,7 @@
         <v>20</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F57" s="10">
         <v>3</v>
@@ -2543,16 +2546,16 @@
         <v>51</v>
       </c>
       <c r="B58" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="D58" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>142</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>143</v>
       </c>
       <c r="F58" s="10">
         <v>2.5</v>
@@ -2563,16 +2566,16 @@
         <v>52</v>
       </c>
       <c r="B59" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="F59" s="10">
         <v>2.5</v>
@@ -2583,24 +2586,24 @@
         <v>53</v>
       </c>
       <c r="B60" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="9" t="s">
         <v>146</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>147</v>
       </c>
       <c r="F60" s="10">
         <v>2.5</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="32" t="s">
-        <v>148</v>
+      <c r="A61" s="34" t="s">
+        <v>147</v>
       </c>
       <c r="B61" s="33"/>
       <c r="C61" s="33"/>
@@ -2613,16 +2616,16 @@
         <v>54</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="D62" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>151</v>
       </c>
       <c r="F62" s="13">
         <v>1.33</v>
@@ -2633,16 +2636,16 @@
         <v>55</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F63" s="13">
         <v>0.08</v>
@@ -2653,16 +2656,16 @@
         <v>56</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>154</v>
+        <v>258</v>
       </c>
       <c r="F64" s="13">
         <v>2.5</v>
@@ -2673,16 +2676,16 @@
         <v>57</v>
       </c>
       <c r="B65" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>157</v>
       </c>
       <c r="F65" s="13">
         <v>1.33</v>
@@ -2693,16 +2696,16 @@
         <v>58</v>
       </c>
       <c r="B66" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="F66" s="10">
         <v>1</v>
@@ -2713,16 +2716,16 @@
         <v>59</v>
       </c>
       <c r="B67" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>163</v>
       </c>
       <c r="F67" s="10">
         <v>1.5</v>
@@ -2733,16 +2736,16 @@
         <v>60</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F68" s="10">
         <v>2.5</v>
@@ -2753,24 +2756,24 @@
         <v>61</v>
       </c>
       <c r="B69" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="F69" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="32" t="s">
-        <v>169</v>
+      <c r="A70" s="34" t="s">
+        <v>167</v>
       </c>
       <c r="B70" s="33"/>
       <c r="C70" s="33"/>
@@ -2779,8 +2782,8 @@
       <c r="F70" s="33"/>
     </row>
     <row r="71" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="32" t="s">
-        <v>170</v>
+      <c r="A71" s="34" t="s">
+        <v>168</v>
       </c>
       <c r="B71" s="33"/>
       <c r="C71" s="33"/>
@@ -2793,16 +2796,16 @@
         <v>62</v>
       </c>
       <c r="B72" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="F72" s="10">
         <v>2.5</v>
@@ -2813,16 +2816,16 @@
         <v>63</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>176</v>
+        <v>257</v>
       </c>
       <c r="F73" s="10">
         <v>2.5</v>
@@ -2833,7 +2836,7 @@
         <v>64</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>61</v>
@@ -2842,7 +2845,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="F74" s="10">
         <v>3</v>
@@ -2853,7 +2856,7 @@
         <v>65</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>61</v>
@@ -2862,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="F75" s="10">
         <v>2</v>
@@ -2873,7 +2876,7 @@
         <v>66</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C76" s="9" t="s">
         <v>61</v>
@@ -2882,7 +2885,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>182</v>
+        <v>254</v>
       </c>
       <c r="F76" s="10">
         <v>3</v>
@@ -2893,7 +2896,7 @@
         <v>67</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>61</v>
@@ -2902,10 +2905,10 @@
         <v>20</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
       <c r="F77" s="10">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -2913,7 +2916,7 @@
         <v>68</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>61</v>
@@ -2922,7 +2925,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F78" s="10">
         <v>3</v>
@@ -2933,7 +2936,7 @@
         <v>69</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C79" s="9" t="s">
         <v>61</v>
@@ -2942,7 +2945,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F79" s="10">
         <v>3</v>
@@ -2953,16 +2956,16 @@
         <v>70</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F80" s="13">
         <v>1.17</v>
@@ -2973,16 +2976,16 @@
         <v>71</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F81" s="16">
         <v>1.25</v>
@@ -2993,16 +2996,16 @@
         <v>72</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F82" s="16">
         <v>1.25</v>
@@ -3013,16 +3016,16 @@
         <v>73</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F83" s="16">
         <v>1.25</v>
@@ -3033,16 +3036,16 @@
         <v>74</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F84" s="13">
         <v>1.17</v>
@@ -3053,16 +3056,16 @@
         <v>75</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F85" s="16">
         <v>1.75</v>
@@ -3073,16 +3076,16 @@
         <v>76</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F86" s="16">
         <v>1.33</v>
@@ -3093,19 +3096,19 @@
         <v>77</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F87" s="10">
-        <v>0.33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3113,16 +3116,16 @@
         <v>78</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F88" s="10">
         <v>2.5</v>
@@ -3133,7 +3136,7 @@
         <v>79</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>48</v>
@@ -3142,7 +3145,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F89" s="10">
         <v>2.5</v>
@@ -3153,16 +3156,16 @@
         <v>80</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F90" s="10">
         <v>2</v>
@@ -3173,16 +3176,16 @@
         <v>81</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F91" s="10">
         <v>2.25</v>
@@ -3193,19 +3196,19 @@
         <v>82</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F92" s="16">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -3213,104 +3216,104 @@
         <v>83</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="F93" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="17">
         <v>84</v>
       </c>
-      <c r="B94" s="18" t="s">
-        <v>225</v>
+      <c r="B94" s="46">
+        <v>46104</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="F94" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="17">
         <v>85</v>
       </c>
-      <c r="B95" s="18" t="s">
-        <v>228</v>
+      <c r="B95" s="46">
+        <v>46105</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F95" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="17">
+      <c r="A96" s="8">
         <v>86</v>
       </c>
-      <c r="B96" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="C96" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="D96" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="E96" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="F96" s="19">
-        <v>3</v>
+      <c r="B96" s="47">
+        <v>46105</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F96" s="10">
+        <v>1.5</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="8">
-        <v>87</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C97" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E97" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="F97" s="10">
-        <v>1.5</v>
+      <c r="A97" s="17">
+        <v>86</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="F97" s="19">
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="32" t="s">
-        <v>235</v>
+      <c r="A98" s="34" t="s">
+        <v>218</v>
       </c>
       <c r="B98" s="33"/>
       <c r="C98" s="33"/>
@@ -3319,8 +3322,8 @@
       <c r="F98" s="33"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" s="42" t="s">
-        <v>236</v>
+      <c r="A99" s="41" t="s">
+        <v>219</v>
       </c>
       <c r="B99" s="33"/>
       <c r="C99" s="33"/>
@@ -3328,12 +3331,12 @@
       <c r="E99" s="33"/>
       <c r="F99" s="20">
         <f>SUM(F4:F98)</f>
-        <v>187.54999999999998</v>
+        <v>188.21999999999997</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="44" t="s">
-        <v>237</v>
+      <c r="A101" s="35" t="s">
+        <v>220</v>
       </c>
       <c r="B101" s="33"/>
       <c r="C101" s="33"/>
@@ -3342,8 +3345,8 @@
       <c r="F101" s="33"/>
     </row>
     <row r="102" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="35" t="s">
-        <v>238</v>
+      <c r="A102" s="43" t="s">
+        <v>221</v>
       </c>
       <c r="B102" s="33"/>
       <c r="C102" s="33"/>
@@ -3352,8 +3355,8 @@
       <c r="F102" s="33"/>
     </row>
     <row r="103" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="40" t="s">
-        <v>239</v>
+      <c r="A103" s="39" t="s">
+        <v>222</v>
       </c>
       <c r="B103" s="33"/>
       <c r="C103" s="33"/>
@@ -3362,8 +3365,8 @@
       <c r="F103" s="33"/>
     </row>
     <row r="104" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="38" t="s">
-        <v>240</v>
+      <c r="A104" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="B104" s="33"/>
       <c r="C104" s="33"/>
@@ -3372,8 +3375,8 @@
       <c r="F104" s="33"/>
     </row>
     <row r="105" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="41" t="s">
-        <v>241</v>
+      <c r="A105" s="40" t="s">
+        <v>224</v>
       </c>
       <c r="B105" s="33"/>
       <c r="C105" s="33"/>
@@ -3382,8 +3385,8 @@
       <c r="F105" s="33"/>
     </row>
     <row r="106" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="34" t="s">
-        <v>242</v>
+      <c r="A106" s="42" t="s">
+        <v>225</v>
       </c>
       <c r="B106" s="33"/>
       <c r="C106" s="33"/>
@@ -3392,8 +3395,8 @@
       <c r="F106" s="33"/>
     </row>
     <row r="107" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="37" t="s">
-        <v>243</v>
+      <c r="A107" s="36" t="s">
+        <v>226</v>
       </c>
       <c r="B107" s="33"/>
       <c r="C107" s="33"/>
@@ -3402,8 +3405,8 @@
       <c r="F107" s="33"/>
     </row>
     <row r="108" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="43" t="s">
-        <v>244</v>
+      <c r="A108" s="32" t="s">
+        <v>227</v>
       </c>
       <c r="B108" s="33"/>
       <c r="C108" s="33"/>
@@ -3413,25 +3416,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A108:F108"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="A107:F107"/>
     <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A105:F105"/>
-    <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A106:F106"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A98:F98"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3450,15 +3453,15 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="45" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
-        <v>246</v>
+      <c r="A2" s="38" t="s">
+        <v>229</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -3475,7 +3478,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -3486,10 +3489,10 @@
         <v>34</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34.5" x14ac:dyDescent="0.35">
@@ -3497,13 +3500,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34.5" x14ac:dyDescent="0.35">
@@ -3511,13 +3514,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -3525,13 +3528,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -3539,13 +3542,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -3553,13 +3556,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="23" x14ac:dyDescent="0.35">
@@ -3570,10 +3573,10 @@
         <v>63</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="23" x14ac:dyDescent="0.35">
@@ -3581,13 +3584,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
